--- a/seed/sources.xlsx
+++ b/seed/sources.xlsx
@@ -29,12 +29,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,7 +56,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,12 +424,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,6 +450,1126 @@
           <t>Региональный</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Постов за 7 дней (проверка 19.10.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://vk.com/krasnoyarskkr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Власть · Правительство Красноярского края</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://vk.com/krasnoyarskrf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Власть · Город Красноярск</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://vk.com/tsur24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Власть · ЦУР Красноярского края</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://vk.com/dgh_krsk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Власть · ДЖКХИБ Администрации Красноярска</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://vk.com/mz_kk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Власть · Министерство здравоохранения Красноярского края</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://vk.com/minobr_krsk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Власть · Министерство образования Красноярского края</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://vk.com/mintrans_kk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Власть · Министерство транспорта Красноярского края</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://vk.com/24rospotrebnadzor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Власть · Роспотребнадзор по Красноярскому краю</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://vk.com/gibdd24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Безопасность · 24_Госавтоинспекция</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://vk.com/mchs24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Безопасность · ГУ МЧС России по Красноярскому краю</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://vk.com/mvd24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Безопасность · Полиция Красноярья</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://vk.com/agochs_krsk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Безопасность · Агентство по ГО, ЧС и ПБ Красноярского края</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://vk.com/news_ngs24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>СМИ · НГС24.РУ | Новости</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://vk.com/newslabru</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>СМИ · Newslab.ru</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://vk.com/sibnovostiru</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>СМИ · sibnovosti.ru</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://vk.com/gornovostikrsk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>СМИ · Городские новости | Красноярск</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://vk.com/delakrasnoyarsk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>СМИ · ДЕЛА Красноярск</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://vk.com/aif_krsk</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>СМИ · АиФ - Красноярск новости</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://vk.com/gazeta_nkk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>СМИ · Наш Красноярский край | Главное</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://vk.com/tvknew</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>СМИ · ТВК Красноярск</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://vk.com/eniseytvchannel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>СМИ · Телеканал Енисей</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://vk.com/trk7ru</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>СМИ · 7 канал Красноярск</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://vk.com/8kanalkrsk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>СМИ · 8 канал - Красноярский край</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://vk.com/vesti_krsk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>СМИ · Вести-Красноярск</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://vk.com/prima_tv</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>СМИ · Прима</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://vk.com/krasnoyarsknewsnet</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>СМИ · Лента новостей Красноярска</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://vk.com/kraschp</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Городские паблики · ЧП Красноярск</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://vk.com/chp_krsk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Городские паблики · ЧП | ДТП Красноярск</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://vk.com/chpkrsk24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Городские паблики · ЧП Красноярский край | Новости | ДТП</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://vk.com/incident_124</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Городские паблики · Инцидент Красноярск</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://vk.com/crime_krsk</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Городские паблики · Криминальный Красноярск</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://vk.com/krasghest</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Городские паблики · «Жесть Красноярска»</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://vk.com/live_kras</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Городские паблики · Я живу в Красноярске</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://vk.com/krasnoyarsk_kray</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Городские паблики · Красноярск live</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://vk.com/liveinkras</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Городские паблики · Живой Красноярск</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://vk.com/krasnoyarsk_1ive</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Городские паблики · Красноярск</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://vk.com/krsk_overhear</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Городские паблики · Подслушано в Красноярске</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://vk.com/krsk_bus</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Городские паблики · Подслушано Красноярск</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://vk.com/norilsk_group</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Города края · Норильск</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://vk.com/sgnorilsk</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Города края · Северный город || Норильск</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://vk.com/tv_osa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Города края · «ОСА» новости Ачинска и Красноярского края</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://vk.com/chpachinsk</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Города края · ЧП Ачинск | Новости</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://vk.com/kvgazeta</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Города края · Канские ведомости</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://vk.com/kansknews</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Города края · НОВОСТИ КАНСКА</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://vk.com/chpkansk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Города края · ЧП Канск | Новости</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://vk.com/city_minusinsk</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Города края · Город Минусинск | новости</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://vk.com/minusinsksreda24</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Города края · Среда24 | Новости Минусинск</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://vk.com/localtime26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Города края · Наши новости. Железногорск</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://vk.com/gorodovoy26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Города края · Городовой, Железногорск</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://vk.com/spektrbogu</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Города края · Новости Богучанского округа</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://ok.ru/gornovosti</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OK · Городские новости Красноярска</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://ok.ru/delakrasnoyarsk</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OK · ДЕЛА – новости Красноярска</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://ok.ru/group/57451052466232</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OK · Телеканал Енисей</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
